--- a/Data/Spreadsheets/street_signs_taipei_sheets.xlsx
+++ b/Data/Spreadsheets/street_signs_taipei_sheets.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omistaja\Desktop\AS Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omistaja\Desktop\AS Project\Data\Spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184EEE92-1A36-4F55-8C2E-BF1FBBCBECF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4ABFFF8-9A0D-46C1-BCDA-67A51E37CA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="4" xr2:uid="{0F63E304-0F8B-433D-B1DF-377F2FBE8827}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="2" xr2:uid="{0F63E304-0F8B-433D-B1DF-377F2FBE8827}"/>
   </bookViews>
   <sheets>
     <sheet name="SIGN" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>sign_id</t>
   </si>
@@ -130,6 +130,39 @@
   </si>
   <si>
     <t>survey_notes</t>
+  </si>
+  <si>
+    <t>S0001</t>
+  </si>
+  <si>
+    <t>Testing.</t>
+  </si>
+  <si>
+    <t>S0002</t>
+  </si>
+  <si>
+    <t>Testing some more.</t>
+  </si>
+  <si>
+    <t>sign_location</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>Taiwan</t>
+  </si>
+  <si>
+    <t>O0001</t>
+  </si>
+  <si>
+    <t>13.8.2026</t>
+  </si>
+  <si>
+    <t>Imaginary</t>
+  </si>
+  <si>
+    <t>S001</t>
   </si>
 </sst>
 </file>
@@ -180,10 +213,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,18 +555,44 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -575,18 +635,18 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -608,6 +668,23 @@
       </c>
       <c r="J1" s="2" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.58888888888888891</v>
+      </c>
+      <c r="H2" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Spreadsheets/street_signs_taipei_sheets.xlsx
+++ b/Data/Spreadsheets/street_signs_taipei_sheets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omistaja\Desktop\AS Project\Data\Spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4ABFFF8-9A0D-46C1-BCDA-67A51E37CA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E9B8E4-AE01-439D-83FA-91DC3AB6F9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="2" xr2:uid="{0F63E304-0F8B-433D-B1DF-377F2FBE8827}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{0F63E304-0F8B-433D-B1DF-377F2FBE8827}"/>
   </bookViews>
   <sheets>
     <sheet name="SIGN" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <si>
     <t>sign_id</t>
   </si>
@@ -132,37 +132,10 @@
     <t>survey_notes</t>
   </si>
   <si>
-    <t>S0001</t>
-  </si>
-  <si>
-    <t>Testing.</t>
-  </si>
-  <si>
-    <t>S0002</t>
-  </si>
-  <si>
-    <t>Testing some more.</t>
-  </si>
-  <si>
     <t>sign_location</t>
   </si>
   <si>
-    <t>Finland</t>
-  </si>
-  <si>
-    <t>Taiwan</t>
-  </si>
-  <si>
-    <t>O0001</t>
-  </si>
-  <si>
-    <t>13.8.2026</t>
-  </si>
-  <si>
-    <t>Imaginary</t>
-  </si>
-  <si>
-    <t>S001</t>
+    <t>comap_link</t>
   </si>
 </sst>
 </file>
@@ -555,7 +528,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -563,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>17</v>
@@ -571,28 +544,6 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -605,10 +556,10 @@
   <sheetPr>
     <tabColor theme="3" tint="0.749992370372631"/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -622,6 +573,9 @@
         <v>27</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -635,7 +589,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -671,21 +625,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.58888888888888891</v>
-      </c>
-      <c r="H2" t="s">
-        <v>38</v>
-      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="E3" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -742,32 +685,35 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>23</v>
       </c>
     </row>
